--- a/grc_wisdom_api/scripts/verify/_tmp/RCM.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp/RCM.xlsx
@@ -47,7 +47,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -59,7 +59,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1172-20260923105942</t>
+    <t>97EF-20260924223621</t>
   </si>
   <si>
     <t>DRAFT — this engagement is Planned. Figures are provisional and the conclusion is not final.</t>
